--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:36</t>
+    <t xml:space="preserve">2026-09-09 22:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:22</t>
+    <t xml:space="preserve">2026-09-12 19:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:39</t>
+    <t xml:space="preserve">2026-09-24 00:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:16</t>
+    <t xml:space="preserve">2026-09-27 22:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:06</t>
+    <t xml:space="preserve">2026-09-29 11:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>26.6</v>
+        <v>265.96</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>26.24</v>
+        <v>262.35</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20.35</v>
+        <v>203.54</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>20.03</v>
+        <v>200.32</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16.87</v>
+        <v>168.67</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16.86</v>
+        <v>168.55</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13.94</v>
+        <v>139.37</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>12.09</v>
+        <v>120.94</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>10.25</v>
+        <v>102.47</v>
       </c>
     </row>
     <row r="11">
@@ -661,7 +661,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8.62</v>
+        <v>86.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:00</t>
+    <t xml:space="preserve">2026-10-01 19:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:25</t>
+    <t xml:space="preserve">2026-10-02 13:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:09</t>
+    <t xml:space="preserve">2026-10-04 07:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2020_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 07:55</t>
+    <t xml:space="preserve">2026-10-05 07:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
